--- a/data_lake/industry/CFM/Channel SSD.xlsx
+++ b/data_lake/industry/CFM/Channel SSD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0EEC1B4-81DB-4902-AF85-254BEBD3B250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5D6F6D5-491F-42DA-B762-F3F734B7768A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -75,32 +75,32 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="7">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="180" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="181" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -109,9 +109,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -133,49 +138,49 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="181" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="쉼표" xfId="1" builtinId="3"/>
@@ -458,19 +463,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.8984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.3984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -493,7 +499,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -516,7 +522,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -539,7 +545,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -562,7 +568,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -585,7 +591,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -608,7 +614,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -631,7 +637,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -654,7 +660,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -677,7 +683,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -700,7 +706,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -723,7 +729,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -746,7 +752,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -769,7 +775,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -792,7 +798,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -815,7 +821,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -838,7 +844,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -861,7 +867,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -884,7 +890,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -907,7 +913,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -930,7 +936,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -953,7 +959,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -976,7 +982,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -999,7 +1005,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -1022,7 +1028,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -1045,7 +1051,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -1068,7 +1074,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -1091,7 +1097,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -1114,7 +1120,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -1137,7 +1143,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -1160,7 +1166,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -1183,7 +1189,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -1206,7 +1212,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -1229,7 +1235,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -1252,7 +1258,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -1275,7 +1281,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -1298,7 +1304,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -1321,7 +1327,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -1344,7 +1350,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -1367,7 +1373,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -1390,7 +1396,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -1413,7 +1419,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -1436,7 +1442,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -1459,7 +1465,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -1482,7 +1488,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -1505,7 +1511,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -1528,7 +1534,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -1551,7 +1557,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -1571,6 +1577,121 @@
         <v>17.7</v>
       </c>
       <c r="G48" s="9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="9">
+        <v>16</v>
+      </c>
+      <c r="F49" s="9">
+        <v>17.7</v>
+      </c>
+      <c r="G49" s="9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="9">
+        <v>16</v>
+      </c>
+      <c r="F50" s="9">
+        <v>17.7</v>
+      </c>
+      <c r="G50" s="9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="9">
+        <v>16</v>
+      </c>
+      <c r="F51" s="9">
+        <v>17.7</v>
+      </c>
+      <c r="G51" s="9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="9">
+        <v>16</v>
+      </c>
+      <c r="F52" s="9">
+        <v>17.7</v>
+      </c>
+      <c r="G52" s="9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="9">
+        <v>16</v>
+      </c>
+      <c r="F53" s="9">
+        <v>17.7</v>
+      </c>
+      <c r="G53" s="9">
         <v>17</v>
       </c>
     </row>
@@ -1582,19 +1703,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A82D123-E18C-4733-B397-9C03328A1E65}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.8984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.3984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1617,7 +1739,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -1640,7 +1762,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -1663,7 +1785,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -1686,7 +1808,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -1709,7 +1831,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -1732,7 +1854,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -1755,7 +1877,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -1778,7 +1900,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -1801,7 +1923,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -1824,7 +1946,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -1847,7 +1969,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -1870,7 +1992,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -1893,7 +2015,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -1916,7 +2038,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -1939,7 +2061,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -1962,7 +2084,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -1985,7 +2107,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -2008,7 +2130,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -2031,7 +2153,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -2054,7 +2176,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -2077,7 +2199,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -2100,7 +2222,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -2123,7 +2245,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -2146,7 +2268,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -2169,7 +2291,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -2192,7 +2314,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -2215,7 +2337,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -2238,7 +2360,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -2261,7 +2383,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -2284,7 +2406,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -2307,7 +2429,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -2330,7 +2452,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -2353,7 +2475,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -2376,7 +2498,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -2399,7 +2521,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -2422,7 +2544,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -2445,7 +2567,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -2468,7 +2590,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -2491,7 +2613,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -2514,7 +2636,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -2537,7 +2659,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -2560,7 +2682,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -2583,7 +2705,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -2606,7 +2728,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -2629,7 +2751,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -2652,7 +2774,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -2675,7 +2797,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -2695,6 +2817,121 @@
         <v>37</v>
       </c>
       <c r="G48" s="12">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="12">
+        <v>34</v>
+      </c>
+      <c r="F49" s="12">
+        <v>37</v>
+      </c>
+      <c r="G49" s="12">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="12">
+        <v>34</v>
+      </c>
+      <c r="F50" s="12">
+        <v>37</v>
+      </c>
+      <c r="G50" s="12">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="12">
+        <v>34</v>
+      </c>
+      <c r="F51" s="12">
+        <v>37</v>
+      </c>
+      <c r="G51" s="12">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="12">
+        <v>34</v>
+      </c>
+      <c r="F52" s="12">
+        <v>37</v>
+      </c>
+      <c r="G52" s="12">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="12">
+        <v>34</v>
+      </c>
+      <c r="F53" s="12">
+        <v>37</v>
+      </c>
+      <c r="G53" s="12">
         <v>36</v>
       </c>
     </row>
@@ -2706,19 +2943,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11DEEDA6-23E7-43DF-BF44-327B2DB18A4F}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.8984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.3984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2741,7 +2979,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -2764,7 +3002,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -2787,7 +3025,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -2810,7 +3048,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -2833,7 +3071,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -2856,7 +3094,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -2879,7 +3117,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -2902,7 +3140,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -2925,7 +3163,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -2948,7 +3186,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -2971,7 +3209,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -2994,7 +3232,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -3017,7 +3255,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -3040,7 +3278,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -3063,7 +3301,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -3086,7 +3324,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -3109,7 +3347,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -3132,7 +3370,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -3155,7 +3393,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -3178,7 +3416,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -3201,7 +3439,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -3224,7 +3462,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -3247,7 +3485,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -3270,7 +3508,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -3293,7 +3531,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -3316,7 +3554,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -3339,7 +3577,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -3362,7 +3600,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -3385,7 +3623,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -3408,7 +3646,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -3431,7 +3669,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -3454,7 +3692,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -3477,7 +3715,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -3500,7 +3738,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -3523,7 +3761,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -3546,7 +3784,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -3569,7 +3807,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -3592,7 +3830,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -3615,7 +3853,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -3638,7 +3876,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -3661,7 +3899,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -3684,7 +3922,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -3707,7 +3945,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -3730,7 +3968,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -3753,7 +3991,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -3776,7 +4014,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -3799,7 +4037,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -3819,6 +4057,121 @@
         <v>66</v>
       </c>
       <c r="G48" s="9">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="9">
+        <v>62.5</v>
+      </c>
+      <c r="F49" s="9">
+        <v>66</v>
+      </c>
+      <c r="G49" s="9">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="9">
+        <v>62.5</v>
+      </c>
+      <c r="F50" s="9">
+        <v>66</v>
+      </c>
+      <c r="G50" s="9">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="9">
+        <v>62.5</v>
+      </c>
+      <c r="F51" s="9">
+        <v>66</v>
+      </c>
+      <c r="G51" s="9">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="9">
+        <v>62.5</v>
+      </c>
+      <c r="F52" s="9">
+        <v>66</v>
+      </c>
+      <c r="G52" s="9">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="9">
+        <v>62.5</v>
+      </c>
+      <c r="F53" s="9">
+        <v>66</v>
+      </c>
+      <c r="G53" s="9">
         <v>65</v>
       </c>
     </row>
@@ -3830,19 +4183,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36F96F38-689A-4B46-8DFA-A4944FA7A43B}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="11.21875" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.8984375" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.3984375" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3865,7 +4219,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -3888,7 +4242,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -3911,7 +4265,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -3934,7 +4288,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -3957,7 +4311,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -3980,7 +4334,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -4003,7 +4357,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -4026,7 +4380,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -4049,7 +4403,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -4072,7 +4426,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -4095,7 +4449,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -4118,7 +4472,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -4141,7 +4495,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -4164,7 +4518,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -4187,7 +4541,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -4210,7 +4564,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -4233,7 +4587,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -4256,7 +4610,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -4279,7 +4633,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -4302,7 +4656,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -4325,7 +4679,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -4348,7 +4702,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -4371,7 +4725,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -4394,7 +4748,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -4417,7 +4771,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -4440,7 +4794,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -4463,7 +4817,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -4486,7 +4840,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -4509,7 +4863,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -4532,7 +4886,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -4555,7 +4909,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -4578,7 +4932,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -4601,7 +4955,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -4624,7 +4978,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -4647,7 +5001,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -4670,7 +5024,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -4693,7 +5047,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -4716,7 +5070,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -4739,7 +5093,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -4762,7 +5116,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -4785,7 +5139,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -4808,7 +5162,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -4831,7 +5185,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -4854,7 +5208,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -4877,7 +5231,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -4900,7 +5254,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -4923,7 +5277,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -4943,6 +5297,121 @@
         <v>39</v>
       </c>
       <c r="G48" s="14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="14">
+        <v>37</v>
+      </c>
+      <c r="F49" s="14">
+        <v>39</v>
+      </c>
+      <c r="G49" s="14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="14">
+        <v>37</v>
+      </c>
+      <c r="F50" s="14">
+        <v>39</v>
+      </c>
+      <c r="G50" s="14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="14">
+        <v>37</v>
+      </c>
+      <c r="F51" s="14">
+        <v>39</v>
+      </c>
+      <c r="G51" s="14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="14">
+        <v>37</v>
+      </c>
+      <c r="F52" s="14">
+        <v>39</v>
+      </c>
+      <c r="G52" s="14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="14">
+        <v>37</v>
+      </c>
+      <c r="F53" s="14">
+        <v>39</v>
+      </c>
+      <c r="G53" s="14">
         <v>38</v>
       </c>
     </row>
@@ -4954,19 +5423,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAAF9F8A-7AB5-472F-A579-46036402780F}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4989,7 +5458,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -5012,7 +5481,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -5035,7 +5504,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -5058,7 +5527,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -5081,7 +5550,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -5104,7 +5573,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -5127,7 +5596,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -5150,7 +5619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -5173,7 +5642,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -5196,7 +5665,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -5219,7 +5688,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -5242,7 +5711,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -5265,7 +5734,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -5288,7 +5757,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -5311,7 +5780,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -5334,7 +5803,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -5357,7 +5826,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -5380,7 +5849,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -5403,7 +5872,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -5426,7 +5895,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -5449,7 +5918,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -5472,7 +5941,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -5495,7 +5964,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -5518,7 +5987,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -5541,7 +6010,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -5564,7 +6033,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -5587,7 +6056,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -5610,7 +6079,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -5633,7 +6102,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -5656,7 +6125,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -5679,7 +6148,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -5702,7 +6171,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -5725,7 +6194,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -5748,7 +6217,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -5771,7 +6240,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -5794,7 +6263,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -5817,7 +6286,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -5840,7 +6309,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -5863,7 +6332,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -5886,7 +6355,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -5909,7 +6378,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -5932,7 +6401,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -5955,7 +6424,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -5978,7 +6447,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -6001,7 +6470,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -6024,7 +6493,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -6047,7 +6516,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -6067,6 +6536,121 @@
         <v>76</v>
       </c>
       <c r="G48" s="9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="9">
+        <v>74</v>
+      </c>
+      <c r="F49" s="9">
+        <v>76</v>
+      </c>
+      <c r="G49" s="9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="9">
+        <v>74</v>
+      </c>
+      <c r="F50" s="9">
+        <v>76</v>
+      </c>
+      <c r="G50" s="9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="9">
+        <v>74</v>
+      </c>
+      <c r="F51" s="9">
+        <v>76</v>
+      </c>
+      <c r="G51" s="9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="9">
+        <v>74</v>
+      </c>
+      <c r="F52" s="9">
+        <v>76</v>
+      </c>
+      <c r="G52" s="9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="9">
+        <v>74</v>
+      </c>
+      <c r="F53" s="9">
+        <v>76</v>
+      </c>
+      <c r="G53" s="9">
         <v>75</v>
       </c>
     </row>
@@ -6078,19 +6662,19 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51F1A6FD-F375-4FB8-8C30-C4A005067594}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.69921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6113,7 +6697,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -6136,7 +6720,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -6159,7 +6743,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -6182,7 +6766,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -6205,7 +6789,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -6228,7 +6812,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -6251,7 +6835,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -6274,7 +6858,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -6297,7 +6881,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -6320,7 +6904,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -6343,7 +6927,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -6366,7 +6950,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -6389,7 +6973,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -6412,7 +6996,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -6435,7 +7019,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -6458,7 +7042,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -6481,7 +7065,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -6504,7 +7088,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -6527,7 +7111,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -6550,7 +7134,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -6573,7 +7157,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -6596,7 +7180,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -6619,7 +7203,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -6642,7 +7226,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -6665,7 +7249,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -6688,7 +7272,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -6711,7 +7295,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -6734,7 +7318,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -6757,7 +7341,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -6780,7 +7364,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -6803,7 +7387,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -6826,7 +7410,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -6849,7 +7433,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -6872,7 +7456,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -6895,7 +7479,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -6918,7 +7502,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -6941,7 +7525,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -6964,7 +7548,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -6987,7 +7571,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -7010,7 +7594,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -7033,7 +7617,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -7056,7 +7640,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -7079,7 +7663,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -7102,7 +7686,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -7125,7 +7709,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -7148,7 +7732,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -7171,7 +7755,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -7191,6 +7775,121 @@
         <v>117</v>
       </c>
       <c r="G48" s="12">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="12">
+        <v>115</v>
+      </c>
+      <c r="F49" s="12">
+        <v>117</v>
+      </c>
+      <c r="G49" s="12">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="12">
+        <v>115</v>
+      </c>
+      <c r="F50" s="12">
+        <v>117</v>
+      </c>
+      <c r="G50" s="12">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="12">
+        <v>115</v>
+      </c>
+      <c r="F51" s="12">
+        <v>117</v>
+      </c>
+      <c r="G51" s="12">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="12">
+        <v>115</v>
+      </c>
+      <c r="F52" s="12">
+        <v>117</v>
+      </c>
+      <c r="G52" s="12">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="12">
+        <v>115</v>
+      </c>
+      <c r="F53" s="12">
+        <v>117</v>
+      </c>
+      <c r="G53" s="12">
         <v>116</v>
       </c>
     </row>
@@ -7202,19 +7901,20 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F720D88E-37F2-4EF2-B2CA-01688ACF7295}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.8984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7237,7 +7937,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -7260,7 +7960,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -7283,7 +7983,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -7306,7 +8006,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -7329,7 +8029,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -7352,7 +8052,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -7375,7 +8075,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -7398,7 +8098,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -7421,7 +8121,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -7444,7 +8144,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -7467,7 +8167,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -7490,7 +8190,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -7513,7 +8213,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -7536,7 +8236,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -7559,7 +8259,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -7582,7 +8282,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -7605,7 +8305,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -7628,7 +8328,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -7651,7 +8351,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -7674,7 +8374,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -7697,7 +8397,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -7720,7 +8420,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -7743,7 +8443,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -7766,7 +8466,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -7789,7 +8489,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -7812,7 +8512,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -7835,7 +8535,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -7858,7 +8558,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -7881,7 +8581,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -7904,7 +8604,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -7927,7 +8627,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -7950,7 +8650,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -7973,7 +8673,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -7996,7 +8696,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -8019,7 +8719,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -8042,7 +8742,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -8065,7 +8765,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -8088,7 +8788,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -8111,7 +8811,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -8134,7 +8834,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -8157,7 +8857,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -8180,7 +8880,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -8203,7 +8903,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -8226,7 +8926,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -8249,7 +8949,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -8272,7 +8972,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -8295,7 +8995,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -8315,6 +9015,121 @@
         <v>82</v>
       </c>
       <c r="G48" s="9">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="9">
+        <v>79</v>
+      </c>
+      <c r="F49" s="9">
+        <v>82</v>
+      </c>
+      <c r="G49" s="9">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="9">
+        <v>79</v>
+      </c>
+      <c r="F50" s="9">
+        <v>82</v>
+      </c>
+      <c r="G50" s="9">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="9">
+        <v>79</v>
+      </c>
+      <c r="F51" s="9">
+        <v>82</v>
+      </c>
+      <c r="G51" s="9">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="9">
+        <v>79</v>
+      </c>
+      <c r="F52" s="9">
+        <v>82</v>
+      </c>
+      <c r="G52" s="9">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="9">
+        <v>79</v>
+      </c>
+      <c r="F53" s="9">
+        <v>82</v>
+      </c>
+      <c r="G53" s="9">
         <v>80</v>
       </c>
     </row>
@@ -8326,19 +9141,20 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CD5A656-5B30-45CF-B579-A97C69E643A5}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="11.21875" style="14" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.8984375" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.3984375" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8361,7 +9177,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -8384,7 +9200,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -8407,7 +9223,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -8430,7 +9246,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -8453,7 +9269,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -8476,7 +9292,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -8499,7 +9315,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -8522,7 +9338,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -8545,7 +9361,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -8568,7 +9384,7 @@
         <v>45.3</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -8591,7 +9407,7 @@
         <v>45.3</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -8614,7 +9430,7 @@
         <v>45.3</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -8637,7 +9453,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -8660,7 +9476,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -8683,7 +9499,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -8706,7 +9522,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -8729,7 +9545,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -8752,7 +9568,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -8775,7 +9591,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -8798,7 +9614,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -8821,7 +9637,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -8844,7 +9660,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -8867,7 +9683,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -8890,7 +9706,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -8913,7 +9729,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -8936,7 +9752,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -8959,7 +9775,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -8982,7 +9798,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -9005,7 +9821,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -9028,7 +9844,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -9051,7 +9867,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -9074,7 +9890,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -9097,7 +9913,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -9120,7 +9936,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -9143,7 +9959,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -9166,7 +9982,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -9189,7 +10005,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -9212,7 +10028,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -9235,7 +10051,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -9258,7 +10074,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -9281,7 +10097,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -9304,7 +10120,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -9327,7 +10143,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -9350,7 +10166,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -9373,7 +10189,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -9396,7 +10212,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -9419,7 +10235,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -9439,6 +10255,121 @@
         <v>131</v>
       </c>
       <c r="G48" s="14">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="14">
+        <v>128</v>
+      </c>
+      <c r="F49" s="14">
+        <v>131</v>
+      </c>
+      <c r="G49" s="14">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="14">
+        <v>128</v>
+      </c>
+      <c r="F50" s="14">
+        <v>131</v>
+      </c>
+      <c r="G50" s="14">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="14">
+        <v>128</v>
+      </c>
+      <c r="F51" s="14">
+        <v>131</v>
+      </c>
+      <c r="G51" s="14">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="14">
+        <v>128</v>
+      </c>
+      <c r="F52" s="14">
+        <v>131</v>
+      </c>
+      <c r="G52" s="14">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="14">
+        <v>128</v>
+      </c>
+      <c r="F53" s="14">
+        <v>131</v>
+      </c>
+      <c r="G53" s="14">
         <v>130</v>
       </c>
     </row>
@@ -9450,19 +10381,20 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A3EDF89-A497-4D9B-AE60-D1EDE4F7FB0B}">
-  <dimension ref="A1:G48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="11.21875" style="14" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.8984375" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.3984375" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9485,7 +10417,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -9508,7 +10440,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -9531,7 +10463,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -9554,7 +10486,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -9577,7 +10509,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -9600,7 +10532,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -9623,7 +10555,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -9646,7 +10578,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -9669,7 +10601,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -9692,7 +10624,7 @@
         <v>83.2</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -9715,7 +10647,7 @@
         <v>83.2</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -9738,7 +10670,7 @@
         <v>83.2</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -9761,7 +10693,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -9784,7 +10716,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -9807,7 +10739,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -9830,7 +10762,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -9853,7 +10785,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -9876,7 +10808,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -9899,7 +10831,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -9922,7 +10854,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -9945,7 +10877,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -9968,7 +10900,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -9991,7 +10923,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -10014,7 +10946,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -10037,7 +10969,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -10060,7 +10992,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -10083,7 +11015,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -10106,7 +11038,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -10129,7 +11061,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -10152,7 +11084,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -10175,7 +11107,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -10198,7 +11130,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -10221,7 +11153,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -10244,7 +11176,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -10267,7 +11199,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -10290,7 +11222,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -10313,7 +11245,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -10336,7 +11268,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -10359,7 +11291,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -10382,7 +11314,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -10405,7 +11337,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -10428,7 +11360,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -10451,7 +11383,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -10474,7 +11406,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -10497,7 +11429,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -10520,7 +11452,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -10543,7 +11475,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -10563,6 +11495,121 @@
         <v>254</v>
       </c>
       <c r="G48" s="14">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="14">
+        <v>247</v>
+      </c>
+      <c r="F49" s="14">
+        <v>254</v>
+      </c>
+      <c r="G49" s="14">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="14">
+        <v>247</v>
+      </c>
+      <c r="F50" s="14">
+        <v>254</v>
+      </c>
+      <c r="G50" s="14">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="14">
+        <v>247</v>
+      </c>
+      <c r="F51" s="14">
+        <v>254</v>
+      </c>
+      <c r="G51" s="14">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="14">
+        <v>247</v>
+      </c>
+      <c r="F52" s="14">
+        <v>254</v>
+      </c>
+      <c r="G52" s="14">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="14">
+        <v>247</v>
+      </c>
+      <c r="F53" s="14">
+        <v>254</v>
+      </c>
+      <c r="G53" s="14">
         <v>250</v>
       </c>
     </row>
